--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0002T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>9.173674870137457</v>
+        <v>1.490722166397337</v>
       </c>
       <c r="D2" t="n">
-        <v>10.23592413781106</v>
+        <v>1.663337672394297</v>
       </c>
       <c r="E2" t="n">
-        <v>9.883190300858631</v>
+        <v>1.606018423889528</v>
       </c>
       <c r="F2" t="n">
-        <v>9.30041108303905</v>
+        <v>1.511316800993846</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.7204311731473</v>
+        <v>6.779570065636436</v>
       </c>
       <c r="D3" t="n">
-        <v>41.13038456443782</v>
+        <v>6.683687491721146</v>
       </c>
       <c r="E3" t="n">
-        <v>9.883190300858631</v>
+        <v>1.606018423889528</v>
       </c>
       <c r="F3" t="n">
-        <v>9.30041108303905</v>
+        <v>1.511316800993846</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.50578827780545</v>
+        <v>5.119690595143386</v>
       </c>
       <c r="D4" t="n">
-        <v>30.80519811652892</v>
+        <v>5.005844693935949</v>
       </c>
       <c r="E4" t="n">
-        <v>9.883190300858631</v>
+        <v>1.606018423889528</v>
       </c>
       <c r="F4" t="n">
-        <v>9.30041108303905</v>
+        <v>1.511316800993846</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.11141318014101</v>
+        <v>6.355604641772915</v>
       </c>
       <c r="D5" t="n">
-        <v>39.47985041800246</v>
+        <v>6.4154756929254</v>
       </c>
       <c r="E5" t="n">
-        <v>9.883190300858631</v>
+        <v>1.606018423889528</v>
       </c>
       <c r="F5" t="n">
-        <v>9.30041108303905</v>
+        <v>1.511316800993846</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.92527187788216</v>
+        <v>4.375356680155851</v>
       </c>
       <c r="D6" t="n">
-        <v>26.0774326601458</v>
+        <v>4.237582807273693</v>
       </c>
       <c r="E6" t="n">
-        <v>9.883190300858631</v>
+        <v>1.606018423889528</v>
       </c>
       <c r="F6" t="n">
-        <v>9.30041108303905</v>
+        <v>1.511316800993846</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>22.14087424490924</v>
+        <v>3.597892064797751</v>
       </c>
       <c r="D7" t="n">
-        <v>22.60274122234999</v>
+        <v>3.672945448631874</v>
       </c>
       <c r="E7" t="n">
-        <v>9.883190300858631</v>
+        <v>1.606018423889528</v>
       </c>
       <c r="F7" t="n">
-        <v>9.30041108303905</v>
+        <v>1.511316800993846</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>28.08840413372984</v>
+        <v>4.5643656717311</v>
       </c>
       <c r="D8" t="n">
-        <v>27.71043360084521</v>
+        <v>4.502945460137346</v>
       </c>
       <c r="E8" t="n">
-        <v>9.883190300858631</v>
+        <v>1.606018423889528</v>
       </c>
       <c r="F8" t="n">
-        <v>9.30041108303905</v>
+        <v>1.511316800993846</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.04683278177237</v>
+        <v>5.69511032703801</v>
       </c>
       <c r="D9" t="n">
-        <v>33.53441669546095</v>
+        <v>5.449342713012405</v>
       </c>
       <c r="E9" t="n">
-        <v>9.883190300858631</v>
+        <v>1.606018423889528</v>
       </c>
       <c r="F9" t="n">
-        <v>9.30041108303905</v>
+        <v>1.511316800993846</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>42.20790018440129</v>
+        <v>6.85878377996521</v>
       </c>
       <c r="D10" t="n">
-        <v>40.46332442278977</v>
+        <v>6.575290218703339</v>
       </c>
       <c r="E10" t="n">
-        <v>9.883190300858631</v>
+        <v>1.606018423889528</v>
       </c>
       <c r="F10" t="n">
-        <v>9.30041108303905</v>
+        <v>1.511316800993846</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.78061075783056</v>
+        <v>6.464349248147466</v>
       </c>
       <c r="D11" t="n">
-        <v>38.59969402198485</v>
+        <v>6.272450278572538</v>
       </c>
       <c r="E11" t="n">
-        <v>9.883190300858631</v>
+        <v>1.606018423889528</v>
       </c>
       <c r="F11" t="n">
-        <v>9.30041108303905</v>
+        <v>1.511316800993846</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
